--- a/artfynd/A 50623-2022 artfynd.xlsx
+++ b/artfynd/A 50623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133334454</v>
       </c>
       <c r="B2" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133334468</v>
       </c>
       <c r="B3" t="n">
-        <v>58291</v>
+        <v>58298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133334414</v>
       </c>
       <c r="B4" t="n">
-        <v>57252</v>
+        <v>57259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>133334509</v>
       </c>
       <c r="B5" t="n">
-        <v>57971</v>
+        <v>57978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50623-2022 artfynd.xlsx
+++ b/artfynd/A 50623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133334454</v>
       </c>
       <c r="B2" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133334468</v>
       </c>
       <c r="B3" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133334414</v>
       </c>
       <c r="B4" t="n">
-        <v>57259</v>
+        <v>57269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>133334509</v>
       </c>
       <c r="B5" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50623-2022 artfynd.xlsx
+++ b/artfynd/A 50623-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133334454</v>
+        <v>133334414</v>
       </c>
       <c r="B2" t="n">
-        <v>58461</v>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133334468</v>
+        <v>133334509</v>
       </c>
       <c r="B3" t="n">
-        <v>58308</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -913,27 +913,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133334414</v>
+        <v>133334484</v>
       </c>
       <c r="B4" t="n">
-        <v>57269</v>
+        <v>58563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>102987</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1032,27 +1032,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133334509</v>
+        <v>133334468</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>58308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1148,6 +1148,125 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133334454</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556583</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6337855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50623-2022 artfynd.xlsx
+++ b/artfynd/A 50623-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334509</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,8 +1292,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>